--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484063_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484063_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.1084</v>
+        <v>9.8688</v>
       </c>
       <c r="E2" t="n">
-        <v>9.0108</v>
+        <v>8.5006</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0977</v>
+        <v>1.3682</v>
       </c>
       <c r="G2" t="n">
         <v>3.5253</v>
@@ -610,13 +610,13 @@
         <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4714</v>
+        <v>-0.7681</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2382</v>
+        <v>-0.272</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2333</v>
+        <v>-0.4962</v>
       </c>
       <c r="V2" t="n">
         <v>7.3101</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9327</v>
+        <v>3.9287</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9573</v>
+        <v>2.1217</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9754</v>
+        <v>1.807</v>
       </c>
       <c r="G3" t="n">
         <v>2.2595</v>
@@ -688,13 +688,13 @@
         <v>2.3806</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9852</v>
+        <v>-0.9892</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3173</v>
+        <v>-0.153</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6679</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>0.6745</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2328</v>
+        <v>3.5273</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1269</v>
+        <v>1.3933</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1059</v>
+        <v>2.134</v>
       </c>
       <c r="G4" t="n">
         <v>1.4976</v>
@@ -766,13 +766,13 @@
         <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8202</v>
+        <v>-0.5258</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8105</v>
+        <v>-0.5441</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0097</v>
+        <v>0.0183</v>
       </c>
       <c r="V4" t="n">
         <v>2.5555</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. MARTINEZ YRANZO</t>
+          <t>D. BUSTO VERANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2843</v>
+        <v>1.4265</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1549</v>
+        <v>1.0163</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1293</v>
+        <v>0.4102</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2915</v>
+        <v>1.6925</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4211</v>
+        <v>2.3481</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1295</v>
+        <v>-0.6556</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2606</v>
+        <v>1.583</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9327</v>
+        <v>2.2581</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3279</v>
+        <v>-0.6751</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9691</v>
+        <v>0.1095</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4883</v>
+        <v>0.09</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4574</v>
+        <v>0.0195</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3968</v>
+        <v>1.1903</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0045</v>
+        <v>-1.1903</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4988</v>
+        <v>-0.5667</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5032</v>
+        <v>-0.6236</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.4085</v>
+        <v>-0.266</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. BUSTO VERANO</t>
+          <t>L. MARTINEZ YRANZO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9458</v>
+        <v>1.172</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6478</v>
+        <v>1.1549</v>
       </c>
       <c r="F6" t="n">
-        <v>0.298</v>
+        <v>0.0171</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6925</v>
+        <v>1.2915</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3481</v>
+        <v>1.4211</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6556</v>
+        <v>-0.1295</v>
       </c>
       <c r="J6" t="n">
-        <v>1.583</v>
+        <v>2.2606</v>
       </c>
       <c r="K6" t="n">
-        <v>2.2581</v>
+        <v>0.9327</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6751</v>
+        <v>1.3279</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1095</v>
+        <v>-0.9691</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09</v>
+        <v>0.4883</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0195</v>
+        <v>-1.4574</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1903</v>
+        <v>0.3968</v>
       </c>
       <c r="Q6" t="n">
+        <v>-0.1984</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.5952</v>
+      </c>
+      <c r="S6" t="n">
+        <v>-0.1077</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.4988</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-0.4085</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-0.4085</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.1903</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-1.671</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.9352</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.7358</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.266</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.266</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9065</v>
+        <v>-0.7662</v>
       </c>
       <c r="E7" t="n">
         <v>-0.756</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1504</v>
+        <v>-0.0102</v>
       </c>
       <c r="G7" t="n">
         <v>2.007</v>
@@ -1000,13 +1000,13 @@
         <v>1.3887</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0685</v>
+        <v>-0.9282</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0679</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0005</v>
+        <v>-0.8603</v>
       </c>
       <c r="V7" t="n">
         <v>0.3373</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0817</v>
+        <v>-1.6929</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5799</v>
+        <v>0.7443</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6616</v>
+        <v>-2.4372</v>
       </c>
       <c r="G8" t="n">
         <v>0.2788</v>
@@ -1078,13 +1078,13 @@
         <v>0.3968</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5508</v>
+        <v>-1.162</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7481</v>
+        <v>-0.5838</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8026</v>
+        <v>-0.5782</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2065</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6685</v>
+        <v>-2.1955</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3684</v>
+        <v>-1.204</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3002</v>
+        <v>-0.9916</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0167</v>
@@ -1156,13 +1156,13 @@
         <v>1.9838</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1125</v>
+        <v>-1.6395</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3173</v>
+        <v>-0.153</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.7952</v>
+        <v>-1.4866</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1425</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.8235</v>
+        <v>-6.9332</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1092</v>
+        <v>-3.4153</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.7142</v>
+        <v>-3.5179</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6281</v>
@@ -1234,13 +1234,13 @@
         <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.71</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0567</v>
+        <v>-0.2493</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.657</v>
+        <v>-0.4606</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4129</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>8.023800000000001</v>
+        <v>8.3355</v>
       </c>
       <c r="E11" t="n">
-        <v>9.244000000000002</v>
+        <v>9.5558</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.220099999999999</v>
+        <v>-1.2204</v>
       </c>
       <c r="G11" t="n">
         <v>10.9074</v>
       </c>
       <c r="H11" t="n">
-        <v>6.1461</v>
+        <v>6.146100000000001</v>
       </c>
       <c r="I11" t="n">
         <v>4.7614</v>
@@ -1288,7 +1288,7 @@
         <v>17.1646</v>
       </c>
       <c r="K11" t="n">
-        <v>7.9669</v>
+        <v>7.966899999999999</v>
       </c>
       <c r="L11" t="n">
         <v>9.1976</v>
@@ -1300,7 +1300,7 @@
         <v>-1.8208</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.4362</v>
+        <v>-4.436199999999999</v>
       </c>
       <c r="P11" t="n">
         <v>-0.9919</v>
@@ -1312,13 +1312,13 @@
         <v>12.895</v>
       </c>
       <c r="S11" t="n">
-        <v>-8.332599999999999</v>
+        <v>-8.020799999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.4002</v>
+        <v>-3.0886</v>
       </c>
       <c r="U11" t="n">
-        <v>-4.9322</v>
+        <v>-4.9324</v>
       </c>
       <c r="V11" t="n">
         <v>6.441000000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.3579</v>
+        <v>6.8732</v>
       </c>
       <c r="E12" t="n">
-        <v>4.8181</v>
+        <v>5.8384</v>
       </c>
       <c r="F12" t="n">
-        <v>1.5398</v>
+        <v>1.0348</v>
       </c>
       <c r="G12" t="n">
         <v>2.8333</v>
@@ -1390,13 +1390,13 @@
         <v>1.9838</v>
       </c>
       <c r="S12" t="n">
-        <v>0.7742</v>
+        <v>1.2895</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5894</v>
+        <v>0.4309</v>
       </c>
       <c r="U12" t="n">
-        <v>1.3636</v>
+        <v>0.8586</v>
       </c>
       <c r="V12" t="n">
         <v>0.7665999999999999</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. OCHOGAVIA CIFRE</t>
+          <t>P. CAMÍ GALERA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6159</v>
+        <v>2.9622</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9716</v>
+        <v>4.2578</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3557</v>
+        <v>-1.2956</v>
       </c>
       <c r="G13" t="n">
-        <v>2.7643</v>
+        <v>2.2522</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8417</v>
+        <v>1.9154</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9227</v>
+        <v>0.3368</v>
       </c>
       <c r="J13" t="n">
-        <v>3.0792</v>
+        <v>2.8933</v>
       </c>
       <c r="K13" t="n">
-        <v>1.7137</v>
+        <v>2.8481</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3655</v>
+        <v>0.0453</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3149</v>
+        <v>-0.6412</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.872</v>
+        <v>-0.9327</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5572</v>
+        <v>0.2916</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5952</v>
+        <v>0.1984</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5952</v>
+        <v>1.1903</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3707</v>
+        <v>0.1743</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5669</v>
+        <v>-0.0566</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1961</v>
+        <v>0.2309</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1143</v>
+        <v>0.3373</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.6745</v>
+        <v>2.4129</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.4398</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. SANCHEZ MORENO</t>
+          <t>M. OCHOGAVIA CIFRE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.432</v>
+        <v>2.8403</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9104</v>
+        <v>2.9716</v>
       </c>
       <c r="F14" t="n">
-        <v>1.5216</v>
+        <v>-0.1313</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.292</v>
+        <v>2.7643</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7504</v>
+        <v>0.8417</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4585</v>
+        <v>1.9227</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2131</v>
+        <v>3.0792</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.3619</v>
+        <v>1.7137</v>
       </c>
       <c r="L14" t="n">
-        <v>0.575</v>
+        <v>1.3655</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5051</v>
+        <v>-0.3149</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3886</v>
+        <v>-0.872</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1165</v>
+        <v>0.5572</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.9838</v>
+        <v>0.5952</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0061</v>
+        <v>0.5952</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6973</v>
+        <v>0.5669</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3089</v>
+        <v>0.0283</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.266</v>
+        <v>-1.1143</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.266</v>
+        <v>-0.4398</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. CAMÍ GALERA</t>
+          <t>L. SANCHEZ MORENO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9495</v>
+        <v>2.3683</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4415</v>
+        <v>0.7064</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.492</v>
+        <v>1.6619</v>
       </c>
       <c r="G15" t="n">
-        <v>2.2522</v>
+        <v>-0.292</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9154</v>
+        <v>-0.7504</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3368</v>
+        <v>0.4585</v>
       </c>
       <c r="J15" t="n">
-        <v>2.8933</v>
+        <v>0.2131</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8481</v>
+        <v>-0.3619</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0453</v>
+        <v>0.575</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6412</v>
+        <v>-0.5051</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9327</v>
+        <v>-0.3886</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2916</v>
+        <v>-0.1165</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1984</v>
+        <v>1.9838</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1903</v>
+        <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8383</v>
+        <v>0.9424</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8728</v>
+        <v>0.4932</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0345</v>
+        <v>0.4491</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3373</v>
+        <v>-0.266</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4129</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-2.0757</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4564</v>
+        <v>-1.3521</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2616</v>
+        <v>0.4251</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8052</v>
+        <v>-1.7772</v>
       </c>
       <c r="G16" t="n">
         <v>0.4916</v>
@@ -1702,13 +1702,13 @@
         <v>0.7935</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2099</v>
+        <v>1.4015</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9136</v>
+        <v>1.077</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2964</v>
+        <v>0.3244</v>
       </c>
       <c r="V16" t="n">
         <v>-2.0548</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.5011</v>
+        <v>-1.3531</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2038</v>
+        <v>0.0002</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2972</v>
+        <v>-1.3533</v>
       </c>
       <c r="G17" t="n">
         <v>-2.5828</v>
@@ -1780,13 +1780,13 @@
         <v>1.3887</v>
       </c>
       <c r="S17" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.2296</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2323</v>
+        <v>-0.0282</v>
       </c>
       <c r="U17" t="n">
-        <v>0.314</v>
+        <v>0.2579</v>
       </c>
       <c r="V17" t="n">
         <v>0.6032</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6473</v>
+        <v>-1.3591</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5903</v>
+        <v>-0.3863</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.057</v>
+        <v>-0.9728</v>
       </c>
       <c r="G18" t="n">
         <v>0.1255</v>
@@ -1858,13 +1858,13 @@
         <v>0.1984</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1309</v>
+        <v>0.1573</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2494</v>
+        <v>-0.0453</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1185</v>
+        <v>0.2026</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8483000000000001</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.693</v>
+        <v>-3.0857</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5884</v>
+        <v>-3.8128</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8954</v>
+        <v>0.7271</v>
       </c>
       <c r="G19" t="n">
         <v>-2.4014</v>
@@ -1936,13 +1936,13 @@
         <v>1.5871</v>
       </c>
       <c r="S19" t="n">
-        <v>3.0167</v>
+        <v>1.624</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3638</v>
+        <v>1.1395</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6529</v>
+        <v>0.4845</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9196</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>T. LLOBERA BIBILONI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.0121</v>
+        <v>-5.2482</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4292</v>
+        <v>-4.4914</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.5829</v>
+        <v>-0.7568</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.9077</v>
+        <v>-2.5893</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.5552</v>
+        <v>-0.8519</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3525</v>
+        <v>-1.7374</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.6585</v>
+        <v>-0.9319</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.8995</v>
+        <v>-0.2568</v>
       </c>
       <c r="L20" t="n">
-        <v>0.241</v>
+        <v>-0.6751</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2492</v>
+        <v>-1.6574</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6558</v>
+        <v>-0.5951</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.5935</v>
+        <v>-1.0623</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9919</v>
+        <v>-2.579</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9919</v>
+        <v>-3.9677</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9838</v>
+        <v>1.3887</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5231</v>
+        <v>0.4521</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0148</v>
+        <v>0.4082</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5084</v>
+        <v>0.0439</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.6194</v>
+        <v>-0.532</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-4.8259</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. LLOBERA BIBILONI</t>
+          <t>X. ANDREU GARI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.9445</v>
+        <v>-5.3235</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.1036</v>
+        <v>-3.5536</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8409</v>
+        <v>-1.77</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.5893</v>
+        <v>-7.6013</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8519</v>
+        <v>-3.3207</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7374</v>
+        <v>-4.2806</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9319</v>
+        <v>-4.9982</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2568</v>
+        <v>-2.3175</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6751</v>
+        <v>-2.6806</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6574</v>
+        <v>-2.6032</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5951</v>
+        <v>-1.0032</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0623</v>
+        <v>-1.6</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.579</v>
+        <v>0.7935</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.9677</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3887</v>
+        <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2443</v>
+        <v>0.2778</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.204</v>
+        <v>0.2381</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0403</v>
+        <v>0.0396</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.532</v>
+        <v>1.2065</v>
       </c>
       <c r="W21" t="n">
+        <v>1.2065</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-0.532</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X. ANDREU GARI</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.0377</v>
+        <v>-5.3462</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.2678</v>
+        <v>-0.7353</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.77</v>
+        <v>-4.6109</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.6013</v>
+        <v>-3.9077</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.3207</v>
+        <v>-2.5552</v>
       </c>
       <c r="I22" t="n">
-        <v>-4.2806</v>
+        <v>-1.3525</v>
       </c>
       <c r="J22" t="n">
-        <v>-4.9982</v>
+        <v>-1.6585</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.3175</v>
+        <v>-1.8995</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.6806</v>
+        <v>0.241</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6032</v>
+        <v>-2.2492</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0032</v>
+        <v>-0.6558</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.6</v>
+        <v>-1.5935</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7935</v>
+        <v>1.9838</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4364</v>
+        <v>1.189</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4761</v>
+        <v>0.7087</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0396</v>
+        <v>0.4803</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2065</v>
+        <v>-3.6194</v>
       </c>
       <c r="W22" t="n">
         <v>1.2065</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-4.8259</v>
       </c>
     </row>
     <row r="23">
@@ -2203,7 +2203,7 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-8.024000000000001</v>
+        <v>-8.023899999999999</v>
       </c>
       <c r="E23" t="n">
         <v>1.2201</v>
@@ -2233,13 +2233,13 @@
         <v>-17.1647</v>
       </c>
       <c r="N23" t="n">
-        <v>-7.966999999999999</v>
+        <v>-7.967</v>
       </c>
       <c r="O23" t="n">
-        <v>-9.1976</v>
+        <v>-9.197600000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9918999999999999</v>
+        <v>0.9918999999999997</v>
       </c>
       <c r="Q23" t="n">
         <v>-12.8949</v>
@@ -2248,16 +2248,16 @@
         <v>13.8868</v>
       </c>
       <c r="S23" t="n">
-        <v>8.332499999999998</v>
+        <v>8.332699999999999</v>
       </c>
       <c r="T23" t="n">
         <v>4.9324</v>
       </c>
       <c r="U23" t="n">
-        <v>3.4004</v>
+        <v>3.400100000000001</v>
       </c>
       <c r="V23" t="n">
-        <v>-6.4408</v>
+        <v>-6.440800000000001</v>
       </c>
       <c r="W23" t="n">
         <v>2.9258</v>
